--- a/Data/PlayerJob.xlsx
+++ b/Data/PlayerJob.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitFolder\ProjectTT\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B1D79C7-50AE-4581-810C-D5293393D298}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EC71F5B-6F99-458B-B84B-FD4D3EFA5DC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,31 +43,31 @@
     <t>1st Job</t>
   </si>
   <si>
-    <t>Attack=20|HP=100|Defence=5</t>
-  </si>
-  <si>
     <t>2nd Job</t>
   </si>
   <si>
-    <t>Attack=50|HP=300|Defence=15</t>
-  </si>
-  <si>
     <t>3rd Job</t>
   </si>
   <si>
-    <t>Attack=100|HP=600|Defence=30</t>
-  </si>
-  <si>
     <t>4th Job</t>
   </si>
   <si>
-    <t>Attack=200|HP=1200|Defence=60</t>
-  </si>
-  <si>
     <t>5th Job</t>
   </si>
   <si>
-    <t>Attack=400|HP=2500|Defence=120</t>
+    <t>Attack=20;HP=100;Defence=5</t>
+  </si>
+  <si>
+    <t>Attack=50;HP=300;Defence=15</t>
+  </si>
+  <si>
+    <t>Attack=100;HP=600;Defence=30</t>
+  </si>
+  <si>
+    <t>Attack=200;HP=1200;Defence=60</t>
+  </si>
+  <si>
+    <t>Attack=400;HP=2500;Defence=120</t>
   </si>
 </sst>
 </file>
@@ -480,7 +480,7 @@
         <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -494,10 +494,10 @@
         <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -511,10 +511,10 @@
         <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -528,10 +528,10 @@
         <v>100</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E6">
         <v>4</v>
@@ -545,7 +545,7 @@
         <v>150</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D7" t="s">
         <v>15</v>
